--- a/角色列表.xlsx
+++ b/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF78BA97-2466-4BEC-960D-2FE608752319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC52B9FA-0705-4002-829E-75071FF5CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1832,40 +1832,40 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2222,7 +2222,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" s="7">
         <v>27</v>
@@ -2239,7 +2239,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="3">
         <f t="shared" ref="L2:L49" si="0">D2*2.2+E2*0.45</f>
-        <v>18.75</v>
+        <v>14.350000000000001</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" ref="M2:M49" si="1">SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0))</f>
@@ -2255,7 +2255,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="8">
         <f t="shared" ref="Q2:Q48" si="2">L2+M2+O2+P2</f>
-        <v>18.75</v>
+        <v>14.350000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="45" x14ac:dyDescent="0.2">
@@ -4492,409 +4492,409 @@
       <c r="Q49" s="3"/>
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="22" t="s">
         <v>195</v>
       </c>
-      <c r="B58" s="15"/>
-      <c r="C58" s="15"/>
-      <c r="D58" s="15"/>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="17" t="s">
+      <c r="A59" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="B60" s="19" t="s">
+      <c r="B60" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="23"/>
     </row>
     <row r="61" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A61" s="23" t="s">
+      <c r="A61" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B61" s="24" t="s">
+      <c r="B61" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="24"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="24"/>
-      <c r="M61" s="24"/>
-      <c r="N61" s="24"/>
-      <c r="O61" s="24"/>
-      <c r="P61" s="24"/>
-      <c r="Q61" s="24"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="19"/>
+      <c r="K61" s="19"/>
+      <c r="L61" s="19"/>
+      <c r="M61" s="19"/>
+      <c r="N61" s="19"/>
+      <c r="O61" s="19"/>
+      <c r="P61" s="19"/>
+      <c r="Q61" s="19"/>
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
-      <c r="A62" s="20" t="s">
+      <c r="A62" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="21" t="s">
+      <c r="B62" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="21"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="21"/>
-      <c r="M62" s="21"/>
-      <c r="N62" s="21"/>
-      <c r="O62" s="21"/>
-      <c r="P62" s="21"/>
-      <c r="Q62" s="21"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="18"/>
+      <c r="E62" s="18"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="18"/>
+      <c r="H62" s="18"/>
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="18"/>
+      <c r="L62" s="18"/>
+      <c r="M62" s="18"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="18"/>
+      <c r="Q62" s="18"/>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="20" t="s">
+      <c r="A63" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B63" s="21" t="s">
+      <c r="B63" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="21"/>
-      <c r="D63" s="21"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="21"/>
-      <c r="H63" s="21"/>
-      <c r="I63" s="21"/>
-      <c r="J63" s="21"/>
-      <c r="K63" s="21"/>
-      <c r="L63" s="21"/>
-      <c r="M63" s="21"/>
-      <c r="N63" s="21"/>
-      <c r="O63" s="21"/>
-      <c r="P63" s="21"/>
-      <c r="Q63" s="21"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="18"/>
+      <c r="E63" s="18"/>
+      <c r="F63" s="18"/>
+      <c r="G63" s="18"/>
+      <c r="H63" s="18"/>
+      <c r="I63" s="18"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="18"/>
+      <c r="L63" s="18"/>
+      <c r="M63" s="18"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="18"/>
+      <c r="Q63" s="18"/>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="20" t="s">
+      <c r="A64" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B64" s="21" t="s">
+      <c r="B64" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
-      <c r="O64" s="21"/>
-      <c r="P64" s="21"/>
-      <c r="Q64" s="21"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18"/>
+      <c r="E64" s="18"/>
+      <c r="F64" s="18"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+      <c r="J64" s="18"/>
+      <c r="K64" s="18"/>
+      <c r="L64" s="18"/>
+      <c r="M64" s="18"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="18"/>
+      <c r="Q64" s="18"/>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="20" t="s">
+      <c r="A65" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="21"/>
-      <c r="O65" s="21"/>
-      <c r="P65" s="21"/>
-      <c r="Q65" s="21"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="18"/>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
+      <c r="H65" s="18"/>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18"/>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18"/>
+      <c r="Q65" s="18"/>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="20" t="s">
+      <c r="A66" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B66" s="21" t="s">
+      <c r="B66" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="C66" s="21"/>
-      <c r="D66" s="21"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="21"/>
-      <c r="G66" s="21"/>
-      <c r="H66" s="21"/>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21"/>
-      <c r="K66" s="21"/>
-      <c r="L66" s="21"/>
-      <c r="M66" s="21"/>
-      <c r="N66" s="21"/>
-      <c r="O66" s="21"/>
-      <c r="P66" s="21"/>
-      <c r="Q66" s="21"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="18"/>
+      <c r="E66" s="18"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="18"/>
+      <c r="H66" s="18"/>
+      <c r="I66" s="18"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="18"/>
+      <c r="L66" s="18"/>
+      <c r="M66" s="18"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="18"/>
+      <c r="Q66" s="18"/>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
+      <c r="C67" s="14"/>
+      <c r="D67" s="14"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A68" s="22" t="s">
+      <c r="A68" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="15"/>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="22"/>
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="A69" s="23" t="s">
+      <c r="A69" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="24"/>
-      <c r="K69" s="24"/>
-      <c r="L69" s="24"/>
-      <c r="M69" s="24"/>
-      <c r="N69" s="24"/>
-      <c r="O69" s="24"/>
-      <c r="P69" s="24"/>
-      <c r="Q69" s="24"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="19"/>
+      <c r="F69" s="19"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="19"/>
+      <c r="K69" s="19"/>
+      <c r="L69" s="19"/>
+      <c r="M69" s="19"/>
+      <c r="N69" s="19"/>
+      <c r="O69" s="19"/>
+      <c r="P69" s="19"/>
+      <c r="Q69" s="19"/>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="20" t="s">
+      <c r="A70" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B70" s="21" t="s">
+      <c r="B70" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="21"/>
-      <c r="D70" s="21"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="21"/>
-      <c r="K70" s="21"/>
-      <c r="L70" s="21"/>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="21"/>
-      <c r="Q70" s="21"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="18"/>
+      <c r="E70" s="18"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="18"/>
+      <c r="L70" s="18"/>
+      <c r="M70" s="18"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="18"/>
+      <c r="Q70" s="18"/>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="20" t="s">
+      <c r="A71" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21"/>
-      <c r="K71" s="21"/>
-      <c r="L71" s="21"/>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="21"/>
-      <c r="Q71" s="21"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+      <c r="H71" s="18"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="18"/>
+      <c r="Q71" s="18"/>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="20" t="s">
+      <c r="A72" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="21"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21"/>
-      <c r="K72" s="21"/>
-      <c r="L72" s="21"/>
-      <c r="M72" s="21"/>
-      <c r="N72" s="21"/>
-      <c r="O72" s="21"/>
-      <c r="P72" s="21"/>
-      <c r="Q72" s="21"/>
+      <c r="C72" s="18"/>
+      <c r="D72" s="18"/>
+      <c r="E72" s="18"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="18"/>
+      <c r="H72" s="18"/>
+      <c r="I72" s="18"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="18"/>
+      <c r="L72" s="18"/>
+      <c r="M72" s="18"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="18"/>
+      <c r="Q72" s="18"/>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="20" t="s">
+      <c r="A73" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B73" s="21" t="s">
+      <c r="B73" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
+      <c r="C73" s="18"/>
+      <c r="D73" s="18"/>
+      <c r="E73" s="18"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="18"/>
+      <c r="H73" s="18"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="18"/>
+      <c r="L73" s="18"/>
+      <c r="M73" s="18"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="18"/>
+      <c r="Q73" s="18"/>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
+      <c r="C74" s="18"/>
+      <c r="D74" s="18"/>
+      <c r="E74" s="18"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="18"/>
+      <c r="H74" s="18"/>
+      <c r="I74" s="18"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="18"/>
+      <c r="L74" s="18"/>
+      <c r="M74" s="18"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="18"/>
+      <c r="Q74" s="18"/>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B75" s="21" t="s">
+      <c r="B75" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
+      <c r="C75" s="18"/>
+      <c r="D75" s="18"/>
+      <c r="E75" s="18"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="18"/>
+      <c r="H75" s="18"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="18"/>
+      <c r="L75" s="18"/>
+      <c r="M75" s="18"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="18"/>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B76" s="21" t="s">
+      <c r="B76" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C76" s="21"/>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
+      <c r="C76" s="18"/>
+      <c r="D76" s="18"/>
+      <c r="E76" s="18"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="18"/>
+      <c r="H76" s="18"/>
+      <c r="I76" s="18"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="18"/>
+      <c r="L76" s="18"/>
+      <c r="M76" s="18"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+      <c r="P76" s="18"/>
+      <c r="Q76" s="18"/>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="20" t="s">
+      <c r="A77" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="21" t="s">
+      <c r="B77" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="C77" s="21"/>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
+      <c r="C77" s="18"/>
+      <c r="D77" s="18"/>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="18"/>
+      <c r="H77" s="18"/>
+      <c r="I77" s="18"/>
+      <c r="J77" s="18"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="18"/>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="25" t="s">
+      <c r="A78" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="25"/>
-      <c r="E78" s="25"/>
-      <c r="F78" s="25"/>
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4903,13 +4903,9 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="B76:Q76"/>
-    <mergeCell ref="B77:Q77"/>
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B73:Q73"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="B64:Q64"/>
     <mergeCell ref="A78:F78"/>
     <mergeCell ref="A68:F68"/>
     <mergeCell ref="B60:F60"/>
@@ -4920,9 +4916,13 @@
     <mergeCell ref="B65:Q65"/>
     <mergeCell ref="B66:Q66"/>
     <mergeCell ref="B70:Q70"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="B76:Q76"/>
+    <mergeCell ref="B77:Q77"/>
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B73:Q73"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4941,12 +4941,12 @@
       <c r="A1" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -4968,12 +4968,12 @@
       <c r="E12">
         <v>18.75</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="H12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
+      <c r="H12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="C13" t="s">

--- a/角色列表.xlsx
+++ b/角色列表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC52B9FA-0705-4002-829E-75071FF5CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CA4CF7-D1E2-4E7B-B871-1A2DB3F53895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11730" yWindow="2100" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色列表" sheetId="1" r:id="rId1"/>
@@ -1843,11 +1843,14 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1855,14 +1858,11 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2222,7 +2222,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="7">
         <v>27</v>
@@ -2239,7 +2239,7 @@
       <c r="K2" s="7"/>
       <c r="L2" s="3">
         <f t="shared" ref="L2:L49" si="0">D2*2.2+E2*0.45</f>
-        <v>14.350000000000001</v>
+        <v>18.75</v>
       </c>
       <c r="M2" s="4">
         <f t="shared" ref="M2:M49" si="1">SUM(IF(ISNUMBER(SEARCH("疾行",F2)),1.5,0), IF(ISNUMBER(SEARCH("渗透",F2)),1.5,0))</f>
@@ -2255,7 +2255,7 @@
       <c r="P2" s="3"/>
       <c r="Q2" s="8">
         <f t="shared" ref="Q2:Q48" si="2">L2+M2+O2+P2</f>
-        <v>14.350000000000001</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="45" x14ac:dyDescent="0.2">
@@ -4492,24 +4492,24 @@
       <c r="Q49" s="3"/>
     </row>
     <row r="58" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="18"/>
+      <c r="E58" s="18"/>
+      <c r="F58" s="18"/>
     </row>
     <row r="59" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="24" t="s">
+      <c r="A59" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
-      <c r="F59" s="24"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
     </row>
     <row r="60" spans="1:17" ht="16.5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
@@ -4527,139 +4527,139 @@
       <c r="A61" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B61" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-      <c r="L61" s="19"/>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
+      <c r="C61" s="24"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="24"/>
+      <c r="N61" s="24"/>
+      <c r="O61" s="24"/>
+      <c r="P61" s="24"/>
+      <c r="Q61" s="24"/>
     </row>
     <row r="62" spans="1:17" ht="18" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="C62" s="18"/>
-      <c r="D62" s="18"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="18"/>
-      <c r="H62" s="18"/>
-      <c r="I62" s="18"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
-      <c r="N62" s="18"/>
-      <c r="O62" s="18"/>
-      <c r="P62" s="18"/>
-      <c r="Q62" s="18"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
     </row>
     <row r="63" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="C63" s="18"/>
-      <c r="D63" s="18"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="18"/>
-      <c r="G63" s="18"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="18"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
-      <c r="N63" s="18"/>
-      <c r="O63" s="18"/>
-      <c r="P63" s="18"/>
-      <c r="Q63" s="18"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
     </row>
     <row r="64" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16" t="s">
         <v>169</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="C64" s="18"/>
-      <c r="D64" s="18"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="18"/>
-      <c r="G64" s="18"/>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18"/>
-      <c r="P64" s="18"/>
-      <c r="Q64" s="18"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="20"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
     </row>
     <row r="65" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="C65" s="18"/>
-      <c r="D65" s="18"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="18"/>
-      <c r="G65" s="18"/>
-      <c r="H65" s="18"/>
-      <c r="I65" s="18"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-      <c r="N65" s="18"/>
-      <c r="O65" s="18"/>
-      <c r="P65" s="18"/>
-      <c r="Q65" s="18"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
     </row>
     <row r="66" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="20" t="s">
         <v>174</v>
       </c>
-      <c r="C66" s="18"/>
-      <c r="D66" s="18"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="18"/>
-      <c r="H66" s="18"/>
-      <c r="I66" s="18"/>
-      <c r="J66" s="18"/>
-      <c r="K66" s="18"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-      <c r="N66" s="18"/>
-      <c r="O66" s="18"/>
-      <c r="P66" s="18"/>
-      <c r="Q66" s="18"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
     </row>
     <row r="67" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="14"/>
@@ -4670,231 +4670,231 @@
       <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:17" ht="27" x14ac:dyDescent="0.2">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="B68" s="22"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="18"/>
+      <c r="E68" s="18"/>
+      <c r="F68" s="18"/>
     </row>
     <row r="69" spans="1:17" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A69" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="B69" s="19" t="s">
+      <c r="B69" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="19"/>
-      <c r="K69" s="19"/>
-      <c r="L69" s="19"/>
-      <c r="M69" s="19"/>
-      <c r="N69" s="19"/>
-      <c r="O69" s="19"/>
-      <c r="P69" s="19"/>
-      <c r="Q69" s="19"/>
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="24"/>
+      <c r="N69" s="24"/>
+      <c r="O69" s="24"/>
+      <c r="P69" s="24"/>
+      <c r="Q69" s="24"/>
     </row>
     <row r="70" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="18"/>
-      <c r="H70" s="18"/>
-      <c r="I70" s="18"/>
-      <c r="J70" s="18"/>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-      <c r="N70" s="18"/>
-      <c r="O70" s="18"/>
-      <c r="P70" s="18"/>
-      <c r="Q70" s="18"/>
+      <c r="C70" s="20"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="20"/>
+      <c r="G70" s="20"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="20"/>
+      <c r="J70" s="20"/>
+      <c r="K70" s="20"/>
+      <c r="L70" s="20"/>
+      <c r="M70" s="20"/>
+      <c r="N70" s="20"/>
+      <c r="O70" s="20"/>
+      <c r="P70" s="20"/>
+      <c r="Q70" s="20"/>
     </row>
     <row r="71" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16" t="s">
         <v>177</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C71" s="18"/>
-      <c r="D71" s="18"/>
-      <c r="E71" s="18"/>
-      <c r="F71" s="18"/>
-      <c r="G71" s="18"/>
-      <c r="H71" s="18"/>
-      <c r="I71" s="18"/>
-      <c r="J71" s="18"/>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-      <c r="N71" s="18"/>
-      <c r="O71" s="18"/>
-      <c r="P71" s="18"/>
-      <c r="Q71" s="18"/>
+      <c r="C71" s="20"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+      <c r="K71" s="20"/>
+      <c r="L71" s="20"/>
+      <c r="M71" s="20"/>
+      <c r="N71" s="20"/>
+      <c r="O71" s="20"/>
+      <c r="P71" s="20"/>
+      <c r="Q71" s="20"/>
     </row>
     <row r="72" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="18"/>
-      <c r="F72" s="18"/>
-      <c r="G72" s="18"/>
-      <c r="H72" s="18"/>
-      <c r="I72" s="18"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-      <c r="N72" s="18"/>
-      <c r="O72" s="18"/>
-      <c r="P72" s="18"/>
-      <c r="Q72" s="18"/>
+      <c r="C72" s="20"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+      <c r="K72" s="20"/>
+      <c r="L72" s="20"/>
+      <c r="M72" s="20"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="20"/>
+      <c r="P72" s="20"/>
+      <c r="Q72" s="20"/>
     </row>
     <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="18"/>
-      <c r="G73" s="18"/>
-      <c r="H73" s="18"/>
-      <c r="I73" s="18"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-      <c r="N73" s="18"/>
-      <c r="O73" s="18"/>
-      <c r="P73" s="18"/>
-      <c r="Q73" s="18"/>
+      <c r="C73" s="20"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+      <c r="K73" s="20"/>
+      <c r="L73" s="20"/>
+      <c r="M73" s="20"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="20"/>
+      <c r="P73" s="20"/>
+      <c r="Q73" s="20"/>
     </row>
     <row r="74" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="18"/>
-      <c r="H74" s="18"/>
-      <c r="I74" s="18"/>
-      <c r="J74" s="18"/>
-      <c r="K74" s="18"/>
-      <c r="L74" s="18"/>
-      <c r="M74" s="18"/>
-      <c r="N74" s="18"/>
-      <c r="O74" s="18"/>
-      <c r="P74" s="18"/>
-      <c r="Q74" s="18"/>
+      <c r="C74" s="20"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+      <c r="K74" s="20"/>
+      <c r="L74" s="20"/>
+      <c r="M74" s="20"/>
+      <c r="N74" s="20"/>
+      <c r="O74" s="20"/>
+      <c r="P74" s="20"/>
+      <c r="Q74" s="20"/>
     </row>
     <row r="75" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C75" s="18"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="18"/>
-      <c r="H75" s="18"/>
-      <c r="I75" s="18"/>
-      <c r="J75" s="18"/>
-      <c r="K75" s="18"/>
-      <c r="L75" s="18"/>
-      <c r="M75" s="18"/>
-      <c r="N75" s="18"/>
-      <c r="O75" s="18"/>
-      <c r="P75" s="18"/>
-      <c r="Q75" s="18"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+      <c r="K75" s="20"/>
+      <c r="L75" s="20"/>
+      <c r="M75" s="20"/>
+      <c r="N75" s="20"/>
+      <c r="O75" s="20"/>
+      <c r="P75" s="20"/>
+      <c r="Q75" s="20"/>
     </row>
     <row r="76" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="C76" s="18"/>
-      <c r="D76" s="18"/>
-      <c r="E76" s="18"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="18"/>
-      <c r="H76" s="18"/>
-      <c r="I76" s="18"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
-      <c r="N76" s="18"/>
-      <c r="O76" s="18"/>
-      <c r="P76" s="18"/>
-      <c r="Q76" s="18"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+      <c r="K76" s="20"/>
+      <c r="L76" s="20"/>
+      <c r="M76" s="20"/>
+      <c r="N76" s="20"/>
+      <c r="O76" s="20"/>
+      <c r="P76" s="20"/>
+      <c r="Q76" s="20"/>
     </row>
     <row r="77" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="18"/>
-      <c r="I77" s="18"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-      <c r="N77" s="18"/>
-      <c r="O77" s="18"/>
-      <c r="P77" s="18"/>
-      <c r="Q77" s="18"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="20"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="20"/>
+      <c r="J77" s="20"/>
+      <c r="K77" s="20"/>
+      <c r="L77" s="20"/>
+      <c r="M77" s="20"/>
+      <c r="N77" s="20"/>
+      <c r="O77" s="20"/>
+      <c r="P77" s="20"/>
+      <c r="Q77" s="20"/>
     </row>
     <row r="78" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="20" t="s">
+      <c r="A78" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="B78" s="20"/>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20"/>
-      <c r="E78" s="20"/>
-      <c r="F78" s="20"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="21"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:S1" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -4903,6 +4903,10 @@
     </sortState>
   </autoFilter>
   <mergeCells count="20">
+    <mergeCell ref="B69:Q69"/>
+    <mergeCell ref="B71:Q71"/>
+    <mergeCell ref="B72:Q72"/>
+    <mergeCell ref="B73:Q73"/>
     <mergeCell ref="A58:F58"/>
     <mergeCell ref="A59:F59"/>
     <mergeCell ref="B64:Q64"/>
@@ -4919,10 +4923,6 @@
     <mergeCell ref="B76:Q76"/>
     <mergeCell ref="B77:Q77"/>
     <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B69:Q69"/>
-    <mergeCell ref="B71:Q71"/>
-    <mergeCell ref="B72:Q72"/>
-    <mergeCell ref="B73:Q73"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/角色列表.xlsx
+++ b/角色列表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game creating\战旗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CA4CF7-D1E2-4E7B-B871-1A2DB3F53895}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52A9461-4787-4702-9B35-2C598B6EB54E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11730" yWindow="2100" windowWidth="16365" windowHeight="14895" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
